--- a/Assets/Excel/PlayerSO.xlsx
+++ b/Assets/Excel/PlayerSO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UNITY\UNITY_PROJECT\TeamProject_CheerUpMyHero\Assets\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\TeamProject_CheerUpMyHero\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{139399F7-0971-496B-9507-3C6C4B842B89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07C6A453-1F5F-4D1F-AEF1-4822F78D50B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Player" sheetId="1" r:id="rId1"/>
@@ -570,7 +570,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="E2" s="2">
         <v>1</v>

--- a/Assets/Excel/PlayerSO.xlsx
+++ b/Assets/Excel/PlayerSO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\TeamProject_CheerUpMyHero\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07C6A453-1F5F-4D1F-AEF1-4822F78D50B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5903A304-7E21-405A-A5EB-C4754761B9F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -582,19 +582,19 @@
         <v>50</v>
       </c>
       <c r="H2" s="1">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="I2" s="1">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="J2" s="3">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="K2" s="1">
-        <v>1</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L2" s="7">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>0</v>
@@ -624,7 +624,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="1">
-        <v>638</v>
+        <v>1638</v>
       </c>
       <c r="E3" s="2">
         <v>1</v>
@@ -636,19 +636,19 @@
         <v>70</v>
       </c>
       <c r="H3" s="1">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="I3" s="1">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="J3" s="3">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="K3" s="1">
-        <v>1</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L3" s="7">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>0</v>
@@ -678,7 +678,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="1">
-        <v>780</v>
+        <v>1780</v>
       </c>
       <c r="E4" s="2">
         <v>1</v>
@@ -690,19 +690,19 @@
         <v>84</v>
       </c>
       <c r="H4" s="1">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="I4" s="1">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="J4" s="3">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="K4" s="1">
-        <v>1</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L4" s="7">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="M4" s="2" t="b">
         <v>0</v>
@@ -732,7 +732,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="1">
-        <v>926</v>
+        <v>1926</v>
       </c>
       <c r="E5" s="2">
         <v>1</v>
@@ -744,19 +744,19 @@
         <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="I5" s="1">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="J5" s="3">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="K5" s="1">
-        <v>1</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L5" s="7">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="M5" s="2" t="b">
         <v>0</v>
@@ -786,7 +786,7 @@
         <v>5</v>
       </c>
       <c r="D6" s="1">
-        <v>1076</v>
+        <v>2076</v>
       </c>
       <c r="E6" s="2">
         <v>1</v>
@@ -798,19 +798,19 @@
         <v>118</v>
       </c>
       <c r="H6" s="1">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="I6" s="1">
-        <v>0.17499999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="J6" s="3">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="K6" s="1">
-        <v>1</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L6" s="7">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="M6" s="2" t="b">
         <v>0</v>
@@ -840,7 +840,7 @@
         <v>6</v>
       </c>
       <c r="D7" s="1">
-        <v>1230</v>
+        <v>2230</v>
       </c>
       <c r="E7" s="2">
         <v>1</v>
@@ -852,19 +852,19 @@
         <v>138</v>
       </c>
       <c r="H7" s="1">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="I7" s="1">
-        <v>0.17499999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="J7" s="3">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="K7" s="1">
-        <v>1</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L7" s="7">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>0</v>
@@ -894,7 +894,7 @@
         <v>7</v>
       </c>
       <c r="D8" s="1">
-        <v>1388</v>
+        <v>2388</v>
       </c>
       <c r="E8" s="2">
         <v>1</v>
@@ -906,19 +906,19 @@
         <v>160</v>
       </c>
       <c r="H8" s="1">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="I8" s="1">
-        <v>0.17499999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="J8" s="3">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="K8" s="1">
-        <v>1</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L8" s="7">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="M8" s="2" t="b">
         <v>0</v>
@@ -948,7 +948,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="1">
-        <v>1550</v>
+        <v>2550</v>
       </c>
       <c r="E9" s="2">
         <v>1</v>
@@ -960,19 +960,19 @@
         <v>184</v>
       </c>
       <c r="H9" s="1">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="I9" s="1">
-        <v>0.17499999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="J9" s="3">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="K9" s="1">
-        <v>1</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L9" s="7">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="M9" s="2" t="b">
         <v>0</v>
@@ -1002,7 +1002,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="1">
-        <v>1716</v>
+        <v>2716</v>
       </c>
       <c r="E10" s="2">
         <v>1</v>
@@ -1014,19 +1014,19 @@
         <v>209</v>
       </c>
       <c r="H10" s="1">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="I10" s="1">
-        <v>0.17499999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="J10" s="3">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="K10" s="1">
-        <v>1</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L10" s="7">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="M10" s="2" t="b">
         <v>0</v>
@@ -1056,7 +1056,7 @@
         <v>10</v>
       </c>
       <c r="D11" s="1">
-        <v>1886</v>
+        <v>2886</v>
       </c>
       <c r="E11" s="2">
         <v>1</v>
@@ -1068,19 +1068,19 @@
         <v>236</v>
       </c>
       <c r="H11" s="1">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="I11" s="1">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J11" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K11" s="1">
-        <v>0.85</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L11" s="7">
-        <v>4.25</v>
+        <v>2.75</v>
       </c>
       <c r="M11" s="2" t="b">
         <v>0</v>
@@ -1110,7 +1110,7 @@
         <v>11</v>
       </c>
       <c r="D12" s="1">
-        <v>2060</v>
+        <v>3060</v>
       </c>
       <c r="E12" s="2">
         <v>1</v>
@@ -1122,19 +1122,19 @@
         <v>265</v>
       </c>
       <c r="H12" s="1">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="I12" s="1">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J12" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K12" s="1">
-        <v>0.85</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L12" s="7">
-        <v>4.25</v>
+        <v>2.75</v>
       </c>
       <c r="M12" s="2" t="b">
         <v>0</v>
@@ -1164,7 +1164,7 @@
         <v>12</v>
       </c>
       <c r="D13" s="1">
-        <v>2240</v>
+        <v>3240</v>
       </c>
       <c r="E13" s="2">
         <v>1</v>
@@ -1176,19 +1176,19 @@
         <v>296</v>
       </c>
       <c r="H13" s="1">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="I13" s="1">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J13" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K13" s="1">
-        <v>0.85</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L13" s="7">
-        <v>4.25</v>
+        <v>2.75</v>
       </c>
       <c r="M13" s="2" t="b">
         <v>0</v>
@@ -1218,7 +1218,7 @@
         <v>13</v>
       </c>
       <c r="D14" s="1">
-        <v>2440</v>
+        <v>3440</v>
       </c>
       <c r="E14" s="2">
         <v>1</v>
@@ -1230,19 +1230,19 @@
         <v>328</v>
       </c>
       <c r="H14" s="1">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="I14" s="1">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J14" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K14" s="1">
-        <v>0.85</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L14" s="7">
-        <v>4.25</v>
+        <v>2.75</v>
       </c>
       <c r="M14" s="2" t="b">
         <v>0</v>
@@ -1272,7 +1272,7 @@
         <v>14</v>
       </c>
       <c r="D15" s="1">
-        <v>2650</v>
+        <v>3650</v>
       </c>
       <c r="E15" s="2">
         <v>1</v>
@@ -1284,19 +1284,19 @@
         <v>363</v>
       </c>
       <c r="H15" s="1">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="I15" s="1">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J15" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" s="1">
-        <v>0.85</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L15" s="7">
-        <v>4.25</v>
+        <v>2.75</v>
       </c>
       <c r="M15" s="2" t="b">
         <v>0</v>
@@ -1326,7 +1326,7 @@
         <v>15</v>
       </c>
       <c r="D16" s="1">
-        <v>2870</v>
+        <v>3870</v>
       </c>
       <c r="E16" s="2">
         <v>1</v>
@@ -1338,19 +1338,19 @@
         <v>404</v>
       </c>
       <c r="H16" s="1">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="I16" s="1">
-        <v>0.22500000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="J16" s="3">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="K16" s="1">
-        <v>0.85</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L16" s="7">
-        <v>4.25</v>
+        <v>2.75</v>
       </c>
       <c r="M16" s="2" t="b">
         <v>0</v>
@@ -1380,7 +1380,7 @@
         <v>16</v>
       </c>
       <c r="D17" s="1">
-        <v>3100</v>
+        <v>4100</v>
       </c>
       <c r="E17" s="2">
         <v>1</v>
@@ -1392,19 +1392,19 @@
         <v>445</v>
       </c>
       <c r="H17" s="1">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="I17" s="1">
-        <v>0.22500000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="J17" s="3">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="K17" s="1">
-        <v>0.85</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L17" s="7">
-        <v>4.25</v>
+        <v>2.75</v>
       </c>
       <c r="M17" s="2" t="b">
         <v>0</v>
@@ -1434,7 +1434,7 @@
         <v>17</v>
       </c>
       <c r="D18" s="1">
-        <v>3350</v>
+        <v>4350</v>
       </c>
       <c r="E18" s="2">
         <v>1</v>
@@ -1446,19 +1446,19 @@
         <v>485</v>
       </c>
       <c r="H18" s="1">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="I18" s="1">
-        <v>0.22500000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="J18" s="3">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="K18" s="1">
-        <v>0.85</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L18" s="7">
-        <v>4.25</v>
+        <v>2.75</v>
       </c>
       <c r="M18" s="2" t="b">
         <v>0</v>
@@ -1488,7 +1488,7 @@
         <v>18</v>
       </c>
       <c r="D19" s="1">
-        <v>3610</v>
+        <v>4610</v>
       </c>
       <c r="E19" s="2">
         <v>1</v>
@@ -1500,19 +1500,19 @@
         <v>529</v>
       </c>
       <c r="H19" s="1">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="I19" s="1">
-        <v>0.22500000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="J19" s="3">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="K19" s="1">
-        <v>0.85</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L19" s="7">
-        <v>4.25</v>
+        <v>2.75</v>
       </c>
       <c r="M19" s="2" t="b">
         <v>0</v>
@@ -1542,7 +1542,7 @@
         <v>19</v>
       </c>
       <c r="D20" s="1">
-        <v>3880</v>
+        <v>4880</v>
       </c>
       <c r="E20" s="2">
         <v>1</v>
@@ -1554,19 +1554,19 @@
         <v>574</v>
       </c>
       <c r="H20" s="1">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="I20" s="1">
-        <v>0.22500000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="J20" s="3">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="K20" s="1">
-        <v>0.85</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L20" s="7">
-        <v>4.25</v>
+        <v>2.75</v>
       </c>
       <c r="M20" s="2" t="b">
         <v>0</v>
@@ -1596,7 +1596,7 @@
         <v>20</v>
       </c>
       <c r="D21" s="1">
-        <v>4160</v>
+        <v>5160</v>
       </c>
       <c r="E21" s="2">
         <v>1</v>
@@ -1608,19 +1608,19 @@
         <v>622</v>
       </c>
       <c r="H21" s="1">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="I21" s="1">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="J21" s="3">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="K21" s="1">
-        <v>0.7</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L21" s="7">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="M21" s="2" t="b">
         <v>0</v>
@@ -1650,7 +1650,7 @@
         <v>21</v>
       </c>
       <c r="D22" s="1">
-        <v>4460</v>
+        <v>5460</v>
       </c>
       <c r="E22" s="2">
         <v>1</v>
@@ -1662,19 +1662,19 @@
         <v>670</v>
       </c>
       <c r="H22" s="1">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="I22" s="1">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="J22" s="3">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="K22" s="1">
-        <v>0.7</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L22" s="7">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="M22" s="2" t="b">
         <v>0</v>
@@ -1704,7 +1704,7 @@
         <v>22</v>
       </c>
       <c r="D23" s="1">
-        <v>4770</v>
+        <v>5770</v>
       </c>
       <c r="E23" s="2">
         <v>1</v>
@@ -1716,19 +1716,19 @@
         <v>722</v>
       </c>
       <c r="H23" s="1">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="I23" s="1">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="J23" s="3">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="K23" s="1">
-        <v>0.7</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L23" s="7">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="M23" s="2" t="b">
         <v>0</v>
@@ -1758,7 +1758,7 @@
         <v>23</v>
       </c>
       <c r="D24" s="1">
-        <v>5100</v>
+        <v>6100</v>
       </c>
       <c r="E24" s="2">
         <v>1</v>
@@ -1770,19 +1770,19 @@
         <v>774</v>
       </c>
       <c r="H24" s="1">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="I24" s="1">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="J24" s="3">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="K24" s="1">
-        <v>0.7</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L24" s="7">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="M24" s="2" t="b">
         <v>0</v>
@@ -1812,7 +1812,7 @@
         <v>24</v>
       </c>
       <c r="D25" s="1">
-        <v>5430</v>
+        <v>6430</v>
       </c>
       <c r="E25" s="2">
         <v>1</v>
@@ -1824,19 +1824,19 @@
         <v>830</v>
       </c>
       <c r="H25" s="1">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="I25" s="1">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="J25" s="3">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="K25" s="1">
-        <v>0.7</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L25" s="7">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="M25" s="2" t="b">
         <v>0</v>
@@ -1866,7 +1866,7 @@
         <v>25</v>
       </c>
       <c r="D26" s="1">
-        <v>5780</v>
+        <v>6780</v>
       </c>
       <c r="E26" s="2">
         <v>1</v>
@@ -1878,19 +1878,19 @@
         <v>886</v>
       </c>
       <c r="H26" s="1">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="I26" s="1">
-        <v>0.27500000000000002</v>
+        <v>0.3</v>
       </c>
       <c r="J26" s="3">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="K26" s="1">
-        <v>0.7</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L26" s="7">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="M26" s="2" t="b">
         <v>0</v>
@@ -1920,7 +1920,7 @@
         <v>26</v>
       </c>
       <c r="D27" s="1">
-        <v>6140</v>
+        <v>7140</v>
       </c>
       <c r="E27" s="2">
         <v>1</v>
@@ -1932,19 +1932,19 @@
         <v>944</v>
       </c>
       <c r="H27" s="1">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="I27" s="1">
-        <v>0.27500000000000002</v>
+        <v>0.3</v>
       </c>
       <c r="J27" s="3">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="K27" s="1">
-        <v>0.7</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L27" s="7">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="M27" s="2" t="b">
         <v>0</v>
@@ -1974,7 +1974,7 @@
         <v>27</v>
       </c>
       <c r="D28" s="1">
-        <v>6510</v>
+        <v>7510</v>
       </c>
       <c r="E28" s="2">
         <v>1</v>
@@ -1986,19 +1986,19 @@
         <v>1005</v>
       </c>
       <c r="H28" s="1">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="I28" s="1">
-        <v>0.27500000000000002</v>
+        <v>0.3</v>
       </c>
       <c r="J28" s="3">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="K28" s="1">
-        <v>0.7</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L28" s="7">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="M28" s="2" t="b">
         <v>0</v>
@@ -2028,7 +2028,7 @@
         <v>28</v>
       </c>
       <c r="D29" s="1">
-        <v>6900</v>
+        <v>7900</v>
       </c>
       <c r="E29" s="2">
         <v>1</v>
@@ -2040,19 +2040,19 @@
         <v>1068</v>
       </c>
       <c r="H29" s="1">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="I29" s="1">
-        <v>0.27500000000000002</v>
+        <v>0.3</v>
       </c>
       <c r="J29" s="3">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="K29" s="1">
-        <v>0.7</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L29" s="7">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="M29" s="2" t="b">
         <v>0</v>
@@ -2082,7 +2082,7 @@
         <v>29</v>
       </c>
       <c r="D30" s="1">
-        <v>7300</v>
+        <v>8300</v>
       </c>
       <c r="E30" s="2">
         <v>1</v>
@@ -2094,19 +2094,19 @@
         <v>1134</v>
       </c>
       <c r="H30" s="1">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="I30" s="1">
-        <v>0.27500000000000002</v>
+        <v>0.3</v>
       </c>
       <c r="J30" s="3">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="K30" s="1">
-        <v>0.7</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L30" s="7">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="M30" s="2" t="b">
         <v>0</v>
@@ -2136,7 +2136,7 @@
         <v>30</v>
       </c>
       <c r="D31" s="1">
-        <v>7710</v>
+        <v>8710</v>
       </c>
       <c r="E31" s="2">
         <v>1</v>
